--- a/backend/uploads/qa_generated/Test_Case_-_Foodsmile_V2_00224a42.xlsx
+++ b/backend/uploads/qa_generated/Test_Case_-_Foodsmile_V2_00224a42.xlsx
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,8 +54,37 @@
       <b val="1"/>
       <sz val="13"/>
     </font>
+    <font>
+      <name val="Browallia New"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="26"/>
+    </font>
+    <font>
+      <name val="Browallia New"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Browallia New"/>
+      <color rgb="00000000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Browallia New"/>
+      <b val="1"/>
+      <color rgb="002E6433"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Browallia New"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -68,8 +97,20 @@
         <bgColor rgb="00CDEEFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007F7F7F"/>
+        <bgColor rgb="007F7F7F"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -91,11 +132,219 @@
         <color rgb="00B0C4DE"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0C4DE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0C4DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0C4DE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0C4DE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0C4DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0C4DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0C4DE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0C4DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+    </border>
+    <border/>
+    <border>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0C4DE"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0C4DE"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0C4DE"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B0C4DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B0C4DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0C4DE"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B0C4DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,6 +372,81 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -488,220 +812,500 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="65" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Introduction</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="B1" s="15" t="n"/>
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="15" t="n"/>
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="15" t="n"/>
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="15" t="n"/>
+      <c r="H3" s="15" t="n"/>
+      <c r="I3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="15" t="n"/>
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n"/>
+      <c r="I4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Introduction</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="16" t="n"/>
+      <c r="G5" s="16" t="n"/>
+      <c r="H5" s="16" t="n"/>
+      <c r="I5" s="16" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>เอกสาร System Testing Template สำหรับทดสอบระบบ FoodSmile อ้างอิงเอกสาร SRS-69-PUT-002 v1.1.0 อย่างเคร่งครัด เอกสารนี้เชื่อมโยงกับ Test Plan หลัก (สภาพแวดล้อมการทดสอบ: Staging/UAT) และใช้กลยุทธ์การจัดการ Test Data แบบ Data Anonymization สำหรับข้อมูลส่วนบุคคล (PDPA) ตามมาตรฐานความปลอดภัย</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="17" t="n"/>
+      <c r="H6" s="17" t="n"/>
+      <c r="I6" s="17" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="17" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+    </row>
+    <row r="8" ht="12" customHeight="1"/>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Author :</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="D9" s="19" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="19" t="n"/>
+      <c r="G9" s="19" t="n"/>
+      <c r="H9" s="19" t="n"/>
+      <c r="I9" s="19" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Version :</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="19" t="n"/>
+      <c r="H10" s="19" t="n"/>
+      <c r="I10" s="19" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Last Updated Date :</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="B11" s="18" t="n"/>
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="D11" s="19" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="19" t="n"/>
+      <c r="G11" s="19" t="n"/>
+      <c r="H11" s="19" t="n"/>
+      <c r="I11" s="19" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Structure of this workbook:</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="16" t="n"/>
+      <c r="I12" s="16" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>This workbook contains the following sheets and forms:</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Introduction</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>สำหรับอธิบายการใช้งานของ Template และแสดงรายละเอียดต่าง ๆ ของ Template</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B13" s="19" t="n"/>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="19" t="n"/>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="19" t="n"/>
+      <c r="G13" s="19" t="n"/>
+      <c r="H13" s="19" t="n"/>
+      <c r="I13" s="19" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Sheet Name</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="n"/>
+      <c r="G14" s="20" t="n"/>
+      <c r="H14" s="20" t="n"/>
+      <c r="I14" s="20" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>Document Change History</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>สำหรับบันทึกประวัติการแก้ไขเอกสารฉบับนี้ในแต่ละเวอร์ชัน (Date, Version, Prepared By)</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="4" t="inlineStr">
+      <c r="F15" s="17" t="n"/>
+      <c r="G15" s="17" t="n"/>
+      <c r="H15" s="17" t="n"/>
+      <c r="I15" s="17" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>Glossary</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="21" t="n"/>
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>สำหรับอธิบายคำศัพท์เฉพาะทาง/ตัวย่อที่ใช้ในเอกสารและระบบ</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="4" t="inlineStr">
+      <c r="F16" s="17" t="n"/>
+      <c r="G16" s="17" t="n"/>
+      <c r="H16" s="17" t="n"/>
+      <c r="I16" s="17" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>Basic Test</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="21" t="n"/>
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>สำหรับการทดสอบเบื้องต้น ประกอบด้วย File List, System Installation, System Configuration</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="4" t="inlineStr">
+      <c r="F17" s="17" t="n"/>
+      <c r="G17" s="17" t="n"/>
+      <c r="H17" s="17" t="n"/>
+      <c r="I17" s="17" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>Execute Test</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="C18" s="21" t="n"/>
+      <c r="D18" s="21" t="n"/>
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>สำหรับสรุปผลการทดสอบระบบ (System Testing) แยกตาม Module/Function พร้อมจำนวน Test Case และเวลาประมาณการ</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="4" t="inlineStr">
+      <c r="F18" s="17" t="n"/>
+      <c r="G18" s="17" t="n"/>
+      <c r="H18" s="17" t="n"/>
+      <c r="I18" s="17" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>Test Case Account Profile</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="C19" s="21" t="n"/>
+      <c r="D19" s="21" t="n"/>
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>สำหรับเขียน Test Case Specification และกรณีทดสอบของ Account &amp; Profile (เข้าสู่ระบบและจัดการบัญชี)</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="4" t="inlineStr">
+      <c r="F19" s="17" t="n"/>
+      <c r="G19" s="17" t="n"/>
+      <c r="H19" s="17" t="n"/>
+      <c r="I19" s="17" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>Test Case Map Search</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="C20" s="21" t="n"/>
+      <c r="D20" s="21" t="n"/>
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>สำหรับเขียน Test Case Specification และกรณีทดสอบของ Map &amp; Search (ค้นหาและแผนที่)</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="4" t="inlineStr">
+      <c r="F20" s="17" t="n"/>
+      <c r="G20" s="17" t="n"/>
+      <c r="H20" s="17" t="n"/>
+      <c r="I20" s="17" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>Test Case Review</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>สำหรับเขียน Test Case Specification และกรณีทดสอบของ Restaurant Review (รีวิวและให้คะแนน)</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="4" t="inlineStr">
+      <c r="F21" s="17" t="n"/>
+      <c r="G21" s="17" t="n"/>
+      <c r="H21" s="17" t="n"/>
+      <c r="I21" s="17" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>Test Case Merchant Onboarding</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>สำหรับเขียน Test Case Specification และกรณีทดสอบของ Merchant Onboarding (ลงทะเบียนร้านค้า)</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="4" t="inlineStr">
+      <c r="F22" s="17" t="n"/>
+      <c r="G22" s="17" t="n"/>
+      <c r="H22" s="17" t="n"/>
+      <c r="I22" s="17" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>Test Case Operating Hours</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>สำหรับเขียน Test Case Specification และกรณีทดสอบของ Operating Hours (จัดการเวลาทำการ)</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="4" t="inlineStr">
+      <c r="F23" s="17" t="n"/>
+      <c r="G23" s="17" t="n"/>
+      <c r="H23" s="17" t="n"/>
+      <c r="I23" s="17" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>Test Case Admin Dashboard</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>สำหรับเขียน Test Case Specification และกรณีทดสอบของ Admin Dashboard (จัดการระบบหลังบ้าน)</t>
         </is>
       </c>
+      <c r="F24" s="17" t="n"/>
+      <c r="G24" s="17" t="n"/>
+      <c r="H24" s="17" t="n"/>
+      <c r="I24" s="17" t="n"/>
+    </row>
+    <row r="25"/>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>Template Change History:</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="20" t="n"/>
+      <c r="H28" s="20" t="n"/>
+      <c r="I28" s="20" t="n"/>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>v.2.0</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>Lead QA Architect</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>สร้าง System Test Case ตามข้อกำหนด SRS FoodSmile จัดระเบียบแยกตามโมดูลและเมนูระบบ</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="n"/>
+      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="17" t="n"/>
+      <c r="I29" s="17" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="38">
+    <mergeCell ref="E21:I21"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="E24:I24"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="E23:I23"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="E14:I14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:I29"/>
+    <mergeCell ref="E20:I20"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="E28:I28"/>
+    <mergeCell ref="E19:I19"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E15:I15"/>
+    <mergeCell ref="E22:I22"/>
+    <mergeCell ref="A1:I4"/>
+    <mergeCell ref="A6:I7"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="E16:I16"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="E18:I18"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -712,365 +1316,575 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L20"/>
+  <dimension ref="B1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+      <c r="J1" s="15" t="n"/>
+      <c r="K1" s="15" t="n"/>
+      <c r="L1" s="15" t="n"/>
+      <c r="M1" s="15" t="n"/>
+      <c r="N1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+      <c r="J2" s="15" t="n"/>
+      <c r="K2" s="15" t="n"/>
+      <c r="L2" s="15" t="n"/>
+      <c r="M2" s="15" t="n"/>
+      <c r="N2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="15" t="n"/>
+      <c r="H3" s="15" t="n"/>
+      <c r="I3" s="15" t="n"/>
+      <c r="J3" s="15" t="n"/>
+      <c r="K3" s="15" t="n"/>
+      <c r="L3" s="15" t="n"/>
+      <c r="M3" s="15" t="n"/>
+      <c r="N3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n"/>
+      <c r="I4" s="15" t="n"/>
+      <c r="J4" s="15" t="n"/>
+      <c r="K4" s="15" t="n"/>
+      <c r="L4" s="15" t="n"/>
+      <c r="M4" s="15" t="n"/>
+      <c r="N4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="29" t="n"/>
+      <c r="I5" s="29" t="n"/>
+      <c r="J5" s="29" t="n"/>
+      <c r="K5" s="29" t="n"/>
+      <c r="L5" s="29" t="n"/>
+      <c r="M5" s="29" t="n"/>
+      <c r="N5" s="30" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="B6" s="31" t="n"/>
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>Project Name :</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>FoodSmile</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="32" t="inlineStr">
         <is>
           <t>Create Date :</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="H6" s="39" t="n"/>
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="14" t="inlineStr">
+      <c r="J6" s="17" t="n"/>
+      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="17" t="n"/>
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="35" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="B7" s="31" t="n"/>
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n"/>
+      <c r="F7" s="34" t="n"/>
+      <c r="G7" s="34" t="n"/>
+      <c r="H7" s="34" t="n"/>
+      <c r="I7" s="34" t="n"/>
+      <c r="J7" s="34" t="n"/>
+      <c r="K7" s="34" t="n"/>
+      <c r="L7" s="34" t="n"/>
+      <c r="M7" s="34" t="n"/>
+      <c r="N7" s="35" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="B8" s="31" t="n"/>
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>Project ID:</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>69-PUT</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>Start Test Date :</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="H8" s="39" t="n"/>
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="14" t="inlineStr">
+      <c r="J8" s="17" t="n"/>
+      <c r="K8" s="17" t="n"/>
+      <c r="L8" s="17" t="n"/>
+      <c r="M8" s="17" t="n"/>
+      <c r="N8" s="35" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="B9" s="31" t="n"/>
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="34" t="n"/>
+      <c r="G9" s="34" t="n"/>
+      <c r="H9" s="34" t="n"/>
+      <c r="I9" s="34" t="n"/>
+      <c r="J9" s="34" t="n"/>
+      <c r="K9" s="34" t="n"/>
+      <c r="L9" s="34" t="n"/>
+      <c r="M9" s="34" t="n"/>
+      <c r="N9" s="35" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="B10" s="31" t="n"/>
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>Tester Name :</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t>Finish Test Date :</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="H10" s="39" t="n"/>
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="C12" s="14" t="inlineStr">
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="17" t="n"/>
+      <c r="L10" s="17" t="n"/>
+      <c r="M10" s="17" t="n"/>
+      <c r="N10" s="35" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+      <c r="H11" s="34" t="n"/>
+      <c r="I11" s="34" t="n"/>
+      <c r="J11" s="34" t="n"/>
+      <c r="K11" s="34" t="n"/>
+      <c r="L11" s="34" t="n"/>
+      <c r="M11" s="34" t="n"/>
+      <c r="N11" s="35" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>Project Release / Version :</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>Module / Function:</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>Merchant Module / Operating Hours (จัดการเวลาทำการ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Module / Function: </t>
+        </is>
+      </c>
+      <c r="H12" s="39" t="n"/>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>Test Case Operating Hours</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="n"/>
+      <c r="K12" s="17" t="n"/>
+      <c r="L12" s="17" t="n"/>
+      <c r="M12" s="17" t="n"/>
+      <c r="N12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="37" t="n"/>
+      <c r="H13" s="37" t="n"/>
+      <c r="I13" s="37" t="n"/>
+      <c r="J13" s="37" t="n"/>
+      <c r="K13" s="37" t="n"/>
+      <c r="L13" s="37" t="n"/>
+      <c r="M13" s="37" t="n"/>
+      <c r="N13" s="38" t="n"/>
+    </row>
+    <row r="14" ht="14" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve"> FUNCTIONAL REQUIREMENTS (Requirements No.) :</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="C15" s="39" t="n"/>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="40" t="inlineStr">
         <is>
           <t>REQ-MCH-002</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="6" t="inlineStr">
+      <c r="F15" s="40" t="n"/>
+      <c r="G15" s="40" t="n"/>
+      <c r="H15" s="40" t="n"/>
+    </row>
+    <row r="16" ht="12" customHeight="1"/>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>Test Case Objective</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>Test Step</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>Automate</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>Req No.</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t>Platforms</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr">
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>Updated By</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="8" t="inlineStr">
+    <row r="18" ht="76" customHeight="1">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>69AA5001</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการตั้งเวลาเปิด-ปิดแบบหลายช่วงเวลา (Split Shift)</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>1. เข้าเมนู 'เวลาทำการ'
 2. กำหนดเวลาเปิด-ปิด วันจันทร์ เป็น 2 ช่วงเวลา
 3. กด 'บันทึก'</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="42" t="inlineStr">
         <is>
           <t>ช่วงที่ 1: 10:00-14:00, ช่วงที่ 2: 17:00-22:00</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="42" t="inlineStr">
         <is>
           <t>ระบบบันทึกเวลา 2 ช่วงสำเร็จ และแสดงสถานะ 'ปิดพักเบรค' หากลูกค้าค้นหาในเวลา 15:00 น.</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="42" t="inlineStr"/>
+      <c r="I18" s="41" t="inlineStr"/>
+      <c r="J18" s="42" t="inlineStr">
         <is>
           <t>[Priority: P1 Critical | Risk Level: Medium]</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="K18" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="L18" s="41" t="inlineStr">
         <is>
           <t>REQ-MCH-002</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="M18" s="41" t="inlineStr">
         <is>
           <t>Web Application</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="N18" s="41" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="8" t="inlineStr">
+    <row r="19" ht="76" customHeight="1">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>69AA5002</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการตั้งวันหยุดพิเศษ (Temporary Closure)</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>1. เข้าเมนู 'เวลาทำการ'
 2. เพิ่มวันหยุดพิเศษ ระบุวันที่เริ่มต้นและสิ้นสุด
 3. กด 'บันทึก'</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="42" t="inlineStr">
         <is>
           <t>วันที่เริ่มต้น: 13 เมษายน, วันที่สิ้นสุด: 15 เมษายน</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="42" t="inlineStr">
         <is>
           <t>ระบบบันทึกวันหยุดพิเศษสำเร็จ และแสดงป้ายกำกับ 'ปิดชั่วคราว' ในช่วงวันดังกล่าว</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H19" s="42" t="inlineStr"/>
+      <c r="I19" s="41" t="inlineStr"/>
+      <c r="J19" s="42" t="inlineStr">
         <is>
           <t>[Priority: P2 Major | Risk Level: Low]</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="K19" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="L19" s="41" t="inlineStr">
         <is>
           <t>REQ-MCH-002</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="M19" s="41" t="inlineStr">
         <is>
           <t>Web Application</t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
+      <c r="N19" s="41" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="8" t="inlineStr">
+    <row r="20" ht="76" customHeight="1">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>69AA5003</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการป้องกันการตั้งเวลาเปิด-ปิดที่ไม่สมเหตุสมผล</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>1. เข้าเมนู 'เวลาทำการ'
 2. กำหนดเวลาเปิดร้านให้อยู่หลังเวลาปิดร้าน
 3. กด 'บันทึก'</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="42" t="inlineStr">
         <is>
           <t>เวลาเปิด: 10:00 น., เวลาปิด: 09:00 น.</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="41" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="42" t="inlineStr">
         <is>
           <t>ระบบแสดงข้อความ 'Error เวลาเปิดร้านต้องอยู่หลังเวลาปิดร้าน' และไม่อนุญาตให้บันทึก</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="42" t="inlineStr"/>
+      <c r="I20" s="41" t="inlineStr"/>
+      <c r="J20" s="42" t="inlineStr">
         <is>
           <t>[Priority: P3 Minor | Risk Level: Low] Validation Test</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="K20" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="L20" s="41" t="inlineStr">
         <is>
           <t>REQ-MCH-002</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="M20" s="41" t="inlineStr">
         <is>
           <t>Web Application</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="N20" s="41" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="I12:M12"/>
+    <mergeCell ref="B1:N4"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:M10"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="D10:F10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1081,423 +1895,635 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L21"/>
+  <dimension ref="B1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+      <c r="J1" s="15" t="n"/>
+      <c r="K1" s="15" t="n"/>
+      <c r="L1" s="15" t="n"/>
+      <c r="M1" s="15" t="n"/>
+      <c r="N1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+      <c r="J2" s="15" t="n"/>
+      <c r="K2" s="15" t="n"/>
+      <c r="L2" s="15" t="n"/>
+      <c r="M2" s="15" t="n"/>
+      <c r="N2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="15" t="n"/>
+      <c r="H3" s="15" t="n"/>
+      <c r="I3" s="15" t="n"/>
+      <c r="J3" s="15" t="n"/>
+      <c r="K3" s="15" t="n"/>
+      <c r="L3" s="15" t="n"/>
+      <c r="M3" s="15" t="n"/>
+      <c r="N3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n"/>
+      <c r="I4" s="15" t="n"/>
+      <c r="J4" s="15" t="n"/>
+      <c r="K4" s="15" t="n"/>
+      <c r="L4" s="15" t="n"/>
+      <c r="M4" s="15" t="n"/>
+      <c r="N4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="29" t="n"/>
+      <c r="I5" s="29" t="n"/>
+      <c r="J5" s="29" t="n"/>
+      <c r="K5" s="29" t="n"/>
+      <c r="L5" s="29" t="n"/>
+      <c r="M5" s="29" t="n"/>
+      <c r="N5" s="30" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="B6" s="31" t="n"/>
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>Project Name :</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>FoodSmile</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="32" t="inlineStr">
         <is>
           <t>Create Date :</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="H6" s="39" t="n"/>
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="14" t="inlineStr">
+      <c r="J6" s="17" t="n"/>
+      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="17" t="n"/>
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="35" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="B7" s="31" t="n"/>
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n"/>
+      <c r="F7" s="34" t="n"/>
+      <c r="G7" s="34" t="n"/>
+      <c r="H7" s="34" t="n"/>
+      <c r="I7" s="34" t="n"/>
+      <c r="J7" s="34" t="n"/>
+      <c r="K7" s="34" t="n"/>
+      <c r="L7" s="34" t="n"/>
+      <c r="M7" s="34" t="n"/>
+      <c r="N7" s="35" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="B8" s="31" t="n"/>
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>Project ID:</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>69-PUT</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>Start Test Date :</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="H8" s="39" t="n"/>
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="14" t="inlineStr">
+      <c r="J8" s="17" t="n"/>
+      <c r="K8" s="17" t="n"/>
+      <c r="L8" s="17" t="n"/>
+      <c r="M8" s="17" t="n"/>
+      <c r="N8" s="35" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="B9" s="31" t="n"/>
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="34" t="n"/>
+      <c r="G9" s="34" t="n"/>
+      <c r="H9" s="34" t="n"/>
+      <c r="I9" s="34" t="n"/>
+      <c r="J9" s="34" t="n"/>
+      <c r="K9" s="34" t="n"/>
+      <c r="L9" s="34" t="n"/>
+      <c r="M9" s="34" t="n"/>
+      <c r="N9" s="35" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="B10" s="31" t="n"/>
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>Tester Name :</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t>Finish Test Date :</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="H10" s="39" t="n"/>
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="C12" s="14" t="inlineStr">
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="17" t="n"/>
+      <c r="L10" s="17" t="n"/>
+      <c r="M10" s="17" t="n"/>
+      <c r="N10" s="35" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+      <c r="H11" s="34" t="n"/>
+      <c r="I11" s="34" t="n"/>
+      <c r="J11" s="34" t="n"/>
+      <c r="K11" s="34" t="n"/>
+      <c r="L11" s="34" t="n"/>
+      <c r="M11" s="34" t="n"/>
+      <c r="N11" s="35" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>Project Release / Version :</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>Module / Function:</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>Admin Module / Admin Dashboard (จัดการระบบหลังบ้าน)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Module / Function: </t>
+        </is>
+      </c>
+      <c r="H12" s="39" t="n"/>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>Test Case Admin Dashboard</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="n"/>
+      <c r="K12" s="17" t="n"/>
+      <c r="L12" s="17" t="n"/>
+      <c r="M12" s="17" t="n"/>
+      <c r="N12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="37" t="n"/>
+      <c r="H13" s="37" t="n"/>
+      <c r="I13" s="37" t="n"/>
+      <c r="J13" s="37" t="n"/>
+      <c r="K13" s="37" t="n"/>
+      <c r="L13" s="37" t="n"/>
+      <c r="M13" s="37" t="n"/>
+      <c r="N13" s="38" t="n"/>
+    </row>
+    <row r="14" ht="14" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve"> FUNCTIONAL REQUIREMENTS (Requirements No.) :</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="C15" s="39" t="n"/>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="40" t="inlineStr">
         <is>
           <t>REQ-ADM-001</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="6" t="inlineStr">
+      <c r="F15" s="40" t="n"/>
+      <c r="G15" s="40" t="n"/>
+      <c r="H15" s="40" t="n"/>
+    </row>
+    <row r="16" ht="12" customHeight="1"/>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>Test Case Objective</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>Test Step</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>Automate</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>Req No.</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t>Platforms</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr">
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>Updated By</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="8" t="inlineStr">
+    <row r="18" ht="95" customHeight="1">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>69AA6001</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการอนุมัติร้านค้า (Approve Merchant KYC)</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>1. เข้าสู่ระบบ Back-office ในฐานะ Admin
 2. ไปที่หน้ารายละเอียดร้านค้าสถานะ Pending
 3. ตรวจสอบเอกสาร KYC และกดปุ่ม 'Approve'</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="42" t="inlineStr">
         <is>
           <t>ร้านค้าที่มีเอกสาร KYC ถูกต้องชัดเจน</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="42" t="inlineStr">
         <is>
           <t>สถานะร้านค้าเปลี่ยนเป็น Approved, ร้านค้าได้รับ Verified Badge, และระบบส่ง Email แจ้ง Merchant</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="42" t="inlineStr"/>
+      <c r="I18" s="41" t="inlineStr"/>
+      <c r="J18" s="42" t="inlineStr">
         <is>
           <t>[Priority: P1 Critical | Risk Level: High]</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="K18" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="L18" s="41" t="inlineStr">
         <is>
           <t>REQ-ADM-001</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="M18" s="41" t="inlineStr">
         <is>
           <t>Web Application</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="N18" s="41" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="8" t="inlineStr">
+    <row r="19" ht="95" customHeight="1">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>69AA6002</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการปฏิเสธเอกสาร KYC (Reject) พร้อมระบุเหตุผล</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>1. ไปที่หน้ารายละเอียดร้านค้าสถานะ Pending
 2. กดปุ่ม 'Reject'
 3. กรอกเหตุผลการปฏิเสธและกดยืนยัน</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="42" t="inlineStr">
         <is>
           <t>เหตุผล: 'รูปถ่ายเอกสารไม่ชัดเจน กรุณาอัปโหลดใหม่'</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="41" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="42" t="inlineStr">
         <is>
           <t>ระบบเปลี่ยนสถานะเป็น Rejected และส่ง Email แจ้งเหตุผลให้ Merchant ทราบ</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H19" s="42" t="inlineStr"/>
+      <c r="I19" s="41" t="inlineStr"/>
+      <c r="J19" s="42" t="inlineStr">
         <is>
           <t>[Priority: P2 Major | Risk Level: Medium]</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="K19" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="L19" s="41" t="inlineStr">
         <is>
           <t>REQ-ADM-001</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="M19" s="41" t="inlineStr">
         <is>
           <t>Web Application</t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
+      <c r="N19" s="41" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="8" t="inlineStr">
+    <row r="20" ht="95" customHeight="1">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>69AA6003</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการซ่อนรีวิวที่ไม่เหมาะสม (Content Moderation)</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>1. ไปที่เมนูจัดการเนื้อหา (Content Moderation)
 2. เลือกรีวิวที่ถูก Report หรือ Flag ไว้
 3. กดปุ่ม 'Hide Review'</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="42" t="inlineStr">
         <is>
           <t>รีวิวที่มีรูปภาพไม่เหมาะสม</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="42" t="inlineStr">
         <is>
           <t>รีวิวดังกล่าวถูกซ่อนจากการแสดงผลในฝั่ง Customer ทันที (Soft Delete)</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="42" t="inlineStr"/>
+      <c r="I20" s="41" t="inlineStr"/>
+      <c r="J20" s="42" t="inlineStr">
         <is>
           <t>[Priority: P2 Major | Risk Level: Medium]</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="K20" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="L20" s="41" t="inlineStr">
         <is>
           <t>REQ-ADM-001</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="M20" s="41" t="inlineStr">
         <is>
           <t>Web Application</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="N20" s="41" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="8" t="inlineStr">
+    <row r="21" ht="76" customHeight="1">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>69AA6004</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบระบบซ่อนรีวิวอัตโนมัติเมื่อถูก Report เกินกำหนด</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="42" t="inlineStr">
         <is>
           <t>1. จำลองผู้ใช้ 5 คน (ไม่ซ้ำกัน) กด Report รีวิวเดียวกันภายใน 24 ชั่วโมง
 2. ตรวจสอบสถานะการแสดงผลของรีวิวนั้นในฝั่ง Customer</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="42" t="inlineStr">
         <is>
           <t>รีวิวเป้าหมาย, จำนวน Report = 5</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="42" t="inlineStr">
         <is>
           <t>ระบบซ่อนรีวิวดังกล่าวอัตโนมัติ และส่งรายการเข้าสู่คิวรอ Admin ตรวจสอบ</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H21" s="42" t="inlineStr"/>
+      <c r="I21" s="41" t="inlineStr"/>
+      <c r="J21" s="42" t="inlineStr">
         <is>
           <t>[Priority: P2 Major | Risk Level: Medium] Automated Action Threshold</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="K21" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="L21" s="41" t="inlineStr">
         <is>
           <t>REQ-ADM-001</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr">
+      <c r="M21" s="41" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="L21" s="8" t="inlineStr">
+      <c r="N21" s="41" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="I12:M12"/>
+    <mergeCell ref="B1:N4"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:M10"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="D10:F10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1508,71 +2534,124 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="65" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Document Change History</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>Document Change History</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="15" t="n"/>
+      <c r="H3" s="15" t="n"/>
+      <c r="I3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n"/>
+      <c r="I4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Document Change History:</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="6" t="inlineStr">
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="22" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>Prepared By</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="E6" s="20" t="n"/>
+      <c r="F6" s="20" t="n"/>
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="8" t="inlineStr">
+      <c r="H6" s="20" t="n"/>
+      <c r="I6" s="20" t="n"/>
+    </row>
+    <row r="7" ht="162" customHeight="1">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>v.2.0</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="E7" s="24" t="n"/>
+      <c r="F7" s="24" t="n"/>
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>1. สร้าง Test Case แยกตามแต่ละเมนูของระบบตามเอกสาร SRS-69-PUT-002 v1.1.0 โครงการ FoodSmile
 2. แก้ไขข้อบกพร่องจาก QA Audit: ระบุรหัสเอกสาร SRS อ้างอิงที่ชัดเจน
@@ -1580,8 +2659,18 @@
 4. เพิ่มการอ้างอิง Test Environment และ Test Data Strategy ในส่วนรายละเอียดเอกสาร</t>
         </is>
       </c>
+      <c r="H7" s="25" t="n"/>
+      <c r="I7" s="25" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="B1:I4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D6:F6"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1592,94 +2681,127 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C10"/>
+  <dimension ref="B1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="75" customWidth="1" min="3" max="3"/>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Glossary</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="6" t="inlineStr">
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>คำศัพท์ (Term)</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>คำอธิบาย (Definition)</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="11" t="inlineStr">
+      <c r="D5" s="20" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>PDPA (Personal Data Protection Act)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>พ.ร.บ. คุ้มครองข้อมูลส่วนบุคคล ระบบต้องมี Consent และรองรับการลบข้อมูล (Right to Erasure)</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="11" t="inlineStr">
+      <c r="D6" s="25" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>PostGIS Bounding Box</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>เทคนิคการค้นหาข้อมูลเชิงพื้นที่ (Spatial Query) ในฐานข้อมูล PostgreSQL เพื่อดึงพิกัดร้านอาหาร</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="11" t="inlineStr">
+      <c r="D7" s="25" t="n"/>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Bayesian Popularity Score</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>สูตรสถิติศาสตร์สำหรับจัดอันดับร้านยอดนิยม เพื่อป้องกันปัญหาร้านที่มีรีวิว 5 ดาวเพียง 1 รีวิว ชนะร้านที่มี 4.5 ดาวแต่มี 1,000 รีวิว</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="11" t="inlineStr">
+      <c r="D8" s="25" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Data Anonymization</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>การทำข้อมูลให้ไม่สามารถระบุตัวตนได้ เช่น การเปลี่ยนชื่อผู้รีวิวเป็น Anonymous User เมื่อมีการลบบัญชี</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="11" t="inlineStr">
+      <c r="D9" s="25" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>KYC (Know Your Customer)</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>กระบวนการยืนยันตัวตนของร้านค้า โดยใช้เอกสารเช่น ภ.พ.20, ทะเบียนการค้า หรือบิลค่าน้ำไฟ</t>
         </is>
       </c>
+      <c r="D10" s="25" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B1:D4"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C8:D8"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1690,70 +2812,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E21"/>
+  <dimension ref="B1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="2" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="65" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Basic Test</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>File List</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="12" t="inlineStr">
+      <c r="C5" s="22" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>File Name</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="D6" s="20" t="n"/>
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="9" t="inlineStr">
+      <c r="F6" s="20" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>ไม่อยู่ในขอบเขตของเอกสารฉบับนี้ — ครอบคลุมเฉพาะ Functional/System Test Case</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="5" t="inlineStr">
+      <c r="F7" s="23" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>System Installation</t>
         </is>
       </c>
+      <c r="C10" s="22" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>Setup Procedures</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="20" t="n"/>
+      <c r="F11" s="20" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>ไม่อยู่ในขอบเขตของเอกสารฉบับนี้</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="12" t="inlineStr">
@@ -1779,6 +2963,44 @@
         </is>
       </c>
     </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>System Configuration</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>Configuration Procedures</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="20" t="n"/>
+      <c r="F16" s="20" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>ไม่อยู่ในขอบเขตของเอกสารฉบับนี้</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
+    </row>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -1811,6 +3033,20 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="B1:F4"/>
+    <mergeCell ref="C11:F11"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1824,321 +3060,389 @@
   <dimension ref="B1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Execute Test</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="15" t="n"/>
+      <c r="H3" s="15" t="n"/>
+      <c r="I3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n"/>
+      <c r="I4" s="15" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>Project Name :</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>FoodSmile</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="4" t="inlineStr">
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Project ID:</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>69-PUT</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="4" t="inlineStr">
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>Project Release / Version :</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="5" t="inlineStr">
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>System Test</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="B14" s="6" t="inlineStr">
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="22" t="n"/>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>REF #</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>Pass
 (Meet criteria for evaluating)*</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="G14" s="20" t="n"/>
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>จำนวน TC</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>เวลาประมาณ (ชม.)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="8" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>User &amp; Customer Module</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>Account &amp; Profile (เข้าสู่ระบบและจัดการบัญชี)</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>ผ่านเกณฑ์การทดสอบตาม Requirement 100%</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>อ้างอิง REQ-USR-001</t>
         </is>
       </c>
-      <c r="H15" s="8" t="n">
+      <c r="G15" s="23" t="n"/>
+      <c r="H15" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="I15" s="23" t="n">
         <v>0.75</v>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="8" t="inlineStr">
+    <row r="16" ht="24" customHeight="1">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>User &amp; Customer Module</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>Map &amp; Search (ค้นหาและแผนที่)</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>ผ่านเกณฑ์การทดสอบตาม Requirement 100%</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>อ้างอิง REQ-SRC-001, REQ-SRC-002</t>
         </is>
       </c>
-      <c r="H16" s="8" t="n">
+      <c r="G16" s="23" t="n"/>
+      <c r="H16" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="I16" s="8" t="n">
+      <c r="I16" s="23" t="n">
         <v>1.25</v>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="8" t="inlineStr">
+    <row r="17" ht="24" customHeight="1">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>User &amp; Customer Module</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>Restaurant Review (รีวิวและให้คะแนน)</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>ผ่านเกณฑ์การทดสอบตาม Requirement 100%</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>อ้างอิง REQ-REV-001</t>
         </is>
       </c>
-      <c r="H17" s="8" t="n">
+      <c r="G17" s="23" t="n"/>
+      <c r="H17" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="I17" s="8" t="n">
+      <c r="I17" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="8" t="inlineStr">
+    <row r="18" ht="24" customHeight="1">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>Merchant Module</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>Merchant Onboarding (ลงทะเบียนร้านค้า)</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>ผ่านเกณฑ์การทดสอบตาม Requirement 100%</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>อ้างอิง REQ-MCH-001</t>
         </is>
       </c>
-      <c r="H18" s="8" t="n">
+      <c r="G18" s="23" t="n"/>
+      <c r="H18" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="I18" s="8" t="n">
+      <c r="I18" s="23" t="n">
         <v>0.75</v>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="8" t="inlineStr">
+    <row r="19" ht="24" customHeight="1">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>Merchant Module</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>Operating Hours (จัดการเวลาทำการ)</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>ผ่านเกณฑ์การทดสอบตาม Requirement 100%</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>อ้างอิง REQ-MCH-002</t>
         </is>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="G19" s="23" t="n"/>
+      <c r="H19" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="I19" s="8" t="n">
+      <c r="I19" s="23" t="n">
         <v>0.75</v>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="8" t="inlineStr">
+    <row r="20" ht="24" customHeight="1">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>Admin Module</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>Admin Dashboard (จัดการระบบหลังบ้าน)</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>ผ่านเกณฑ์การทดสอบตาม Requirement 100%</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>อ้างอิง REQ-ADM-001</t>
         </is>
       </c>
-      <c r="H20" s="8" t="n">
+      <c r="G20" s="23" t="n"/>
+      <c r="H20" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="I20" s="8" t="n">
+      <c r="I20" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="11" t="inlineStr">
+    <row r="21" ht="26" customHeight="1">
+      <c r="B21" s="27" t="inlineStr">
         <is>
           <t>รวม (Total)</t>
         </is>
       </c>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="H21" s="11" t="n">
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="27" t="n"/>
+      <c r="F21" s="27" t="n"/>
+      <c r="G21" s="27" t="n"/>
+      <c r="H21" s="20" t="n">
         <v>22</v>
       </c>
-      <c r="I21" s="11" t="n">
+      <c r="I21" s="20" t="n">
         <v>5.5</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B1:I4"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="D10:F10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2149,199 +3453,386 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L20"/>
+  <dimension ref="B1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+      <c r="J1" s="15" t="n"/>
+      <c r="K1" s="15" t="n"/>
+      <c r="L1" s="15" t="n"/>
+      <c r="M1" s="15" t="n"/>
+      <c r="N1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+      <c r="J2" s="15" t="n"/>
+      <c r="K2" s="15" t="n"/>
+      <c r="L2" s="15" t="n"/>
+      <c r="M2" s="15" t="n"/>
+      <c r="N2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="15" t="n"/>
+      <c r="H3" s="15" t="n"/>
+      <c r="I3" s="15" t="n"/>
+      <c r="J3" s="15" t="n"/>
+      <c r="K3" s="15" t="n"/>
+      <c r="L3" s="15" t="n"/>
+      <c r="M3" s="15" t="n"/>
+      <c r="N3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n"/>
+      <c r="I4" s="15" t="n"/>
+      <c r="J4" s="15" t="n"/>
+      <c r="K4" s="15" t="n"/>
+      <c r="L4" s="15" t="n"/>
+      <c r="M4" s="15" t="n"/>
+      <c r="N4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="29" t="n"/>
+      <c r="I5" s="29" t="n"/>
+      <c r="J5" s="29" t="n"/>
+      <c r="K5" s="29" t="n"/>
+      <c r="L5" s="29" t="n"/>
+      <c r="M5" s="29" t="n"/>
+      <c r="N5" s="30" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="B6" s="31" t="n"/>
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>Project Name :</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>FoodSmile</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="32" t="inlineStr">
         <is>
           <t>Create Date :</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="H6" s="39" t="n"/>
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="14" t="inlineStr">
+      <c r="J6" s="17" t="n"/>
+      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="17" t="n"/>
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="35" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="B7" s="31" t="n"/>
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n"/>
+      <c r="F7" s="34" t="n"/>
+      <c r="G7" s="34" t="n"/>
+      <c r="H7" s="34" t="n"/>
+      <c r="I7" s="34" t="n"/>
+      <c r="J7" s="34" t="n"/>
+      <c r="K7" s="34" t="n"/>
+      <c r="L7" s="34" t="n"/>
+      <c r="M7" s="34" t="n"/>
+      <c r="N7" s="35" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="B8" s="31" t="n"/>
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>Project ID:</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>69-PUT</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>Start Test Date :</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="H8" s="39" t="n"/>
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="14" t="inlineStr">
+      <c r="J8" s="17" t="n"/>
+      <c r="K8" s="17" t="n"/>
+      <c r="L8" s="17" t="n"/>
+      <c r="M8" s="17" t="n"/>
+      <c r="N8" s="35" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="B9" s="31" t="n"/>
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="34" t="n"/>
+      <c r="G9" s="34" t="n"/>
+      <c r="H9" s="34" t="n"/>
+      <c r="I9" s="34" t="n"/>
+      <c r="J9" s="34" t="n"/>
+      <c r="K9" s="34" t="n"/>
+      <c r="L9" s="34" t="n"/>
+      <c r="M9" s="34" t="n"/>
+      <c r="N9" s="35" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="B10" s="31" t="n"/>
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>Tester Name :</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t>Finish Test Date :</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="H10" s="39" t="n"/>
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="C12" s="14" t="inlineStr">
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="17" t="n"/>
+      <c r="L10" s="17" t="n"/>
+      <c r="M10" s="17" t="n"/>
+      <c r="N10" s="35" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+      <c r="H11" s="34" t="n"/>
+      <c r="I11" s="34" t="n"/>
+      <c r="J11" s="34" t="n"/>
+      <c r="K11" s="34" t="n"/>
+      <c r="L11" s="34" t="n"/>
+      <c r="M11" s="34" t="n"/>
+      <c r="N11" s="35" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>Project Release / Version :</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>Module / Function:</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>User &amp; Customer Module / Account &amp; Profile (เข้าสู่ระบบและจัดการบัญชี)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Module / Function: </t>
+        </is>
+      </c>
+      <c r="H12" s="39" t="n"/>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>Test Case Account Profile</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="n"/>
+      <c r="K12" s="17" t="n"/>
+      <c r="L12" s="17" t="n"/>
+      <c r="M12" s="17" t="n"/>
+      <c r="N12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="37" t="n"/>
+      <c r="H13" s="37" t="n"/>
+      <c r="I13" s="37" t="n"/>
+      <c r="J13" s="37" t="n"/>
+      <c r="K13" s="37" t="n"/>
+      <c r="L13" s="37" t="n"/>
+      <c r="M13" s="37" t="n"/>
+      <c r="N13" s="38" t="n"/>
+    </row>
+    <row r="14" ht="14" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve"> FUNCTIONAL REQUIREMENTS (Requirements No.) :</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="C15" s="39" t="n"/>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="40" t="inlineStr">
         <is>
           <t>REQ-USR-001, NFR-SEC-003</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="6" t="inlineStr">
+      <c r="F15" s="40" t="n"/>
+      <c r="G15" s="40" t="n"/>
+      <c r="H15" s="40" t="n"/>
+    </row>
+    <row r="16" ht="12" customHeight="1"/>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>Test Case Objective</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>Test Step</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>Automate</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>Req No.</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t>Platforms</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr">
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>Updated By</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="8" t="inlineStr">
+    <row r="18" ht="133" customHeight="1">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>69AA1001</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการเข้าสู่ระบบสำเร็จเมื่อผู้ใช้ยอมรับเงื่อนไข PDPA</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>1. เปิดแอปพลิเคชันและเลือกช่องทางเข้าสู่ระบบ (เช่น Email/Password)
 2. กรอกข้อมูลที่ถูกต้องและกดเข้าสู่ระบบ
@@ -2349,166 +3840,189 @@
 4. กดยอมรับ (Accept)</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="42" t="inlineStr">
         <is>
           <t>Email: testuser@foodsmile.com, Password: ValidPassword123!</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="42" t="inlineStr">
         <is>
           <t>ระบบสร้าง Session สำเร็จ และนำผู้ใช้เข้าสู่หน้าหลัก (Home Screen) ของแอปพลิเคชัน</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="42" t="inlineStr"/>
+      <c r="I18" s="41" t="inlineStr"/>
+      <c r="J18" s="42" t="inlineStr">
         <is>
           <t>[Priority: P1 Critical | Risk Level: High]</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="K18" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="L18" s="41" t="inlineStr">
         <is>
           <t>REQ-USR-001</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="M18" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="N18" s="41" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="8" t="inlineStr">
+    <row r="19" ht="95" customHeight="1">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>69AA1002</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการปฏิเสธเงื่อนไข PDPA ต้องไม่สามารถเข้าสู่ระบบได้</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>1. เปิดแอปพลิเคชันและเลือกช่องทางเข้าสู่ระบบ
 2. ระบบแสดงหน้าต่าง PDPA Consent
 3. กดปฏิเสธ (Deny)</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="42" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="41" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="42" t="inlineStr">
         <is>
           <t>ระบบบล็อกการเข้าสู่ระบบ แสดงข้อความเตือน 'ระบบไม่สามารถดำเนินการต่อได้ หากไม่ยอมรับเงื่อนไข' และพากลับไปหน้า Guest</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H19" s="42" t="inlineStr"/>
+      <c r="I19" s="41" t="inlineStr"/>
+      <c r="J19" s="42" t="inlineStr">
         <is>
           <t>[Priority: P2 Major | Risk Level: Medium]</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="K19" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="L19" s="41" t="inlineStr">
         <is>
           <t>REQ-USR-001</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="M19" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
+      <c r="N19" s="41" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="8" t="inlineStr">
+    <row r="20" ht="95" customHeight="1">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>69AA1003</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการลบบัญชีผู้ใช้และการทำ Data Anonymization (Right to Erasure)</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>1. เข้าสู่ระบบด้วยบัญชีที่มีประวัติการรีวิว
 2. ไปที่เมนูตั้งค่าบัญชี
 3. กดปุ่ม 'ลบบัญชีผู้ใช้' และยืนยันการลบ</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="42" t="inlineStr">
         <is>
           <t>บัญชีผู้ใช้ที่มีข้อมูลรีวิวร้านอาหาร 1 รายการ</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="42" t="inlineStr">
         <is>
           <t>ระบบลบข้อมูล PII ออกจากฐานข้อมูลถาวร, เปลี่ยนชื่อผู้รีวิวเป็น 'Anonymous User' (Data Anonymization), และบังคับ Log out ทันที</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="42" t="inlineStr"/>
+      <c r="I20" s="41" t="inlineStr"/>
+      <c r="J20" s="42" t="inlineStr">
         <is>
           <t>[Priority: P1 Critical | Risk Level: High] ทดสอบเรื่อง PDPA Compliance</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="K20" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="L20" s="41" t="inlineStr">
         <is>
           <t>REQ-USR-001</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="M20" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="N20" s="41" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="I12:M12"/>
+    <mergeCell ref="B1:N4"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:M10"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="D10:F10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2519,478 +4033,692 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L22"/>
+  <dimension ref="B1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+      <c r="J1" s="15" t="n"/>
+      <c r="K1" s="15" t="n"/>
+      <c r="L1" s="15" t="n"/>
+      <c r="M1" s="15" t="n"/>
+      <c r="N1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+      <c r="J2" s="15" t="n"/>
+      <c r="K2" s="15" t="n"/>
+      <c r="L2" s="15" t="n"/>
+      <c r="M2" s="15" t="n"/>
+      <c r="N2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="15" t="n"/>
+      <c r="H3" s="15" t="n"/>
+      <c r="I3" s="15" t="n"/>
+      <c r="J3" s="15" t="n"/>
+      <c r="K3" s="15" t="n"/>
+      <c r="L3" s="15" t="n"/>
+      <c r="M3" s="15" t="n"/>
+      <c r="N3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n"/>
+      <c r="I4" s="15" t="n"/>
+      <c r="J4" s="15" t="n"/>
+      <c r="K4" s="15" t="n"/>
+      <c r="L4" s="15" t="n"/>
+      <c r="M4" s="15" t="n"/>
+      <c r="N4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="29" t="n"/>
+      <c r="I5" s="29" t="n"/>
+      <c r="J5" s="29" t="n"/>
+      <c r="K5" s="29" t="n"/>
+      <c r="L5" s="29" t="n"/>
+      <c r="M5" s="29" t="n"/>
+      <c r="N5" s="30" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="B6" s="31" t="n"/>
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>Project Name :</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>FoodSmile</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="32" t="inlineStr">
         <is>
           <t>Create Date :</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="H6" s="39" t="n"/>
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="14" t="inlineStr">
+      <c r="J6" s="17" t="n"/>
+      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="17" t="n"/>
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="35" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="B7" s="31" t="n"/>
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n"/>
+      <c r="F7" s="34" t="n"/>
+      <c r="G7" s="34" t="n"/>
+      <c r="H7" s="34" t="n"/>
+      <c r="I7" s="34" t="n"/>
+      <c r="J7" s="34" t="n"/>
+      <c r="K7" s="34" t="n"/>
+      <c r="L7" s="34" t="n"/>
+      <c r="M7" s="34" t="n"/>
+      <c r="N7" s="35" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="B8" s="31" t="n"/>
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>Project ID:</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>69-PUT</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>Start Test Date :</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="H8" s="39" t="n"/>
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="14" t="inlineStr">
+      <c r="J8" s="17" t="n"/>
+      <c r="K8" s="17" t="n"/>
+      <c r="L8" s="17" t="n"/>
+      <c r="M8" s="17" t="n"/>
+      <c r="N8" s="35" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="B9" s="31" t="n"/>
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="34" t="n"/>
+      <c r="G9" s="34" t="n"/>
+      <c r="H9" s="34" t="n"/>
+      <c r="I9" s="34" t="n"/>
+      <c r="J9" s="34" t="n"/>
+      <c r="K9" s="34" t="n"/>
+      <c r="L9" s="34" t="n"/>
+      <c r="M9" s="34" t="n"/>
+      <c r="N9" s="35" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="B10" s="31" t="n"/>
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>Tester Name :</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t>Finish Test Date :</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="H10" s="39" t="n"/>
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="C12" s="14" t="inlineStr">
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="17" t="n"/>
+      <c r="L10" s="17" t="n"/>
+      <c r="M10" s="17" t="n"/>
+      <c r="N10" s="35" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+      <c r="H11" s="34" t="n"/>
+      <c r="I11" s="34" t="n"/>
+      <c r="J11" s="34" t="n"/>
+      <c r="K11" s="34" t="n"/>
+      <c r="L11" s="34" t="n"/>
+      <c r="M11" s="34" t="n"/>
+      <c r="N11" s="35" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>Project Release / Version :</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>Module / Function:</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>User &amp; Customer Module / Map &amp; Search (ค้นหาและแผนที่)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Module / Function: </t>
+        </is>
+      </c>
+      <c r="H12" s="39" t="n"/>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>Test Case Map Search</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="n"/>
+      <c r="K12" s="17" t="n"/>
+      <c r="L12" s="17" t="n"/>
+      <c r="M12" s="17" t="n"/>
+      <c r="N12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="37" t="n"/>
+      <c r="H13" s="37" t="n"/>
+      <c r="I13" s="37" t="n"/>
+      <c r="J13" s="37" t="n"/>
+      <c r="K13" s="37" t="n"/>
+      <c r="L13" s="37" t="n"/>
+      <c r="M13" s="37" t="n"/>
+      <c r="N13" s="38" t="n"/>
+    </row>
+    <row r="14" ht="14" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve"> FUNCTIONAL REQUIREMENTS (Requirements No.) :</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="C15" s="39" t="n"/>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="40" t="inlineStr">
         <is>
           <t>REQ-SRC-001, REQ-SRC-002, NFR-PERF-001</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="6" t="inlineStr">
+      <c r="F15" s="40" t="n"/>
+      <c r="G15" s="40" t="n"/>
+      <c r="H15" s="40" t="n"/>
+    </row>
+    <row r="16" ht="12" customHeight="1"/>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>Test Case Objective</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>Test Step</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>Automate</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>Req No.</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t>Platforms</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr">
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>Updated By</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="8" t="inlineStr">
+    <row r="18" ht="76" customHeight="1">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>69AA2001</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการค้นหาร้านอาหารด้วยพิกัด GPS ปัจจุบันในรัศมีเริ่มต้น</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>1. เปิดแอปพลิเคชันและอนุญาตการเข้าถึง GPS
 2. สังเกตผลลัพธ์บนแผนที่และแบบรายการ</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="42" t="inlineStr">
         <is>
           <t>พิกัด GPS: 13.7563, 100.5018 (กรุงเทพมหานคร)</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="42" t="inlineStr">
         <is>
           <t>ระบบแสดงร้านอาหารในรัศมี 3 กิโลเมตร (Default) บนแผนที่แบบ Interactive และมีการรวมหมุด (Clustering) เมื่อระยะห่าง &lt; 40px</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="42" t="inlineStr"/>
+      <c r="I18" s="41" t="inlineStr"/>
+      <c r="J18" s="42" t="inlineStr">
         <is>
           <t>[Priority: P1 Critical | Risk Level: High]</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="K18" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="L18" s="41" t="inlineStr">
         <is>
           <t>REQ-SRC-001</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="M18" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="N18" s="41" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="8" t="inlineStr">
+    <row r="19" ht="76" customHeight="1">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>69AA2002</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการแสดงป้ายกำกับ 'กำลังจะปิด' เมื่อใช้ตัวกรอง Open Now</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>1. ค้นหาร้านอาหารและเลือกตัวกรอง 'เปิดอยู่ตอนนี้ (Open Now)'
 2. ตรวจสอบร้านค้าที่มีเวลาปิดใกล้เคียงกับเวลาปัจจุบัน (น้อยกว่า 30 นาที)</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="42" t="inlineStr">
         <is>
           <t>เวลาปัจจุบัน 21:30 น., ร้านเป้าหมายปิดเวลา 22:00 น.</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="42" t="inlineStr">
         <is>
           <t>ระบบแสดงร้านค้าในผลลัพธ์ พร้อมแสดงป้ายกำกับ 'กำลังจะปิดในอีก 30 นาที' อย่างถูกต้อง</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H19" s="42" t="inlineStr"/>
+      <c r="I19" s="41" t="inlineStr"/>
+      <c r="J19" s="42" t="inlineStr">
         <is>
           <t>[Priority: P2 Major | Risk Level: Medium] ทดสอบ Boundary Value</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="K19" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="L19" s="41" t="inlineStr">
         <is>
           <t>REQ-SRC-001</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="M19" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
+      <c r="N19" s="41" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="8" t="inlineStr">
+    <row r="20" ht="76" customHeight="1">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>69AA2003</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการทำงานเมื่อผู้ใช้ไม่อนุญาตให้เข้าถึง GPS</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>1. ปิด Location Services ในระดับ OS
 2. เปิดแอปพลิเคชัน FoodSmile</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="42" t="inlineStr">
         <is>
           <t>Location Services = Disabled</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="41" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="42" t="inlineStr">
         <is>
           <t>ระบบแสดงข้อความ 'กรุณาเปิด GPS หรือเลือกพื้นที่ด้วยตนเอง' และแสดงช่องค้นหาพื้นที่ (Manual Area Selection)</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="42" t="inlineStr"/>
+      <c r="I20" s="41" t="inlineStr"/>
+      <c r="J20" s="42" t="inlineStr">
         <is>
           <t>[Priority: P2 Major | Risk Level: Low]</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="K20" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="L20" s="41" t="inlineStr">
         <is>
           <t>REQ-SRC-001</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="M20" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="N20" s="41" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="8" t="inlineStr">
+    <row r="21" ht="76" customHeight="1">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>69AA2004</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบตรรกะการแนะนำร้านอาหารกรณีไม่พบข้อมูล (Fallback Logic)</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="42" t="inlineStr">
         <is>
           <t>1. ค้นหาร้านอาหารด้วยคำค้นหาที่ไม่มีในรัศมี 1 กม.
 2. รอระบบประมวลผล</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="42" t="inlineStr">
         <is>
           <t>คำค้นหา: 'อาหารแปลกประหลาด', รัศมี: 1 กม.</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="42" t="inlineStr">
         <is>
           <t>ระบบแสดงข้อความแจ้งขยายรัศมีเป็น 10 กม. และแสดงร้านอาหารที่เปิดอยู่ เรียงตามคะแนน Bayesian Popularity Score</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H21" s="42" t="inlineStr"/>
+      <c r="I21" s="41" t="inlineStr"/>
+      <c r="J21" s="42" t="inlineStr">
         <is>
           <t>[Priority: P2 Major | Risk Level: Medium]</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="K21" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="L21" s="41" t="inlineStr">
         <is>
           <t>REQ-SRC-002</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr">
+      <c r="M21" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L21" s="8" t="inlineStr">
+      <c r="N21" s="41" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="8" t="inlineStr">
+    <row r="22" ht="76" customHeight="1">
+      <c r="B22" s="41" t="inlineStr">
         <is>
           <t>69AA2005</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบประสิทธิภาพการค้นหาเชิงพิกัด (Spatial Query Performance)</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="42" t="inlineStr">
         <is>
           <t>1. จำลองการส่ง Request ค้นหาเชิงพิกัด (Bounding Box) จำนวน 500 Requests Per Second
 2. วัดค่า Latency ของการตอบกลับ</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="42" t="inlineStr">
         <is>
           <t>Load Test Script (CCU = 1,000)</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G22" s="42" t="inlineStr">
         <is>
           <t>ระบบตอบสนองโดยมีค่า P95 Latency &lt;= 1.5 วินาที และไม่มี API Timeout</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H22" s="42" t="inlineStr"/>
+      <c r="I22" s="41" t="inlineStr"/>
+      <c r="J22" s="42" t="inlineStr">
         <is>
           <t>[Priority: P1 Critical | Risk Level: High] Performance Test</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="K22" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="L22" s="41" t="inlineStr">
         <is>
           <t>NFR-PERF-001</t>
         </is>
       </c>
-      <c r="K22" s="8" t="inlineStr">
+      <c r="M22" s="41" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="L22" s="8" t="inlineStr">
+      <c r="N22" s="41" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="I12:M12"/>
+    <mergeCell ref="B1:N4"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:M10"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="D10:F10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3001,199 +4729,386 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L21"/>
+  <dimension ref="B1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+      <c r="J1" s="15" t="n"/>
+      <c r="K1" s="15" t="n"/>
+      <c r="L1" s="15" t="n"/>
+      <c r="M1" s="15" t="n"/>
+      <c r="N1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+      <c r="J2" s="15" t="n"/>
+      <c r="K2" s="15" t="n"/>
+      <c r="L2" s="15" t="n"/>
+      <c r="M2" s="15" t="n"/>
+      <c r="N2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="15" t="n"/>
+      <c r="H3" s="15" t="n"/>
+      <c r="I3" s="15" t="n"/>
+      <c r="J3" s="15" t="n"/>
+      <c r="K3" s="15" t="n"/>
+      <c r="L3" s="15" t="n"/>
+      <c r="M3" s="15" t="n"/>
+      <c r="N3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n"/>
+      <c r="I4" s="15" t="n"/>
+      <c r="J4" s="15" t="n"/>
+      <c r="K4" s="15" t="n"/>
+      <c r="L4" s="15" t="n"/>
+      <c r="M4" s="15" t="n"/>
+      <c r="N4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="29" t="n"/>
+      <c r="I5" s="29" t="n"/>
+      <c r="J5" s="29" t="n"/>
+      <c r="K5" s="29" t="n"/>
+      <c r="L5" s="29" t="n"/>
+      <c r="M5" s="29" t="n"/>
+      <c r="N5" s="30" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="B6" s="31" t="n"/>
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>Project Name :</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>FoodSmile</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="32" t="inlineStr">
         <is>
           <t>Create Date :</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="H6" s="39" t="n"/>
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="14" t="inlineStr">
+      <c r="J6" s="17" t="n"/>
+      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="17" t="n"/>
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="35" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="B7" s="31" t="n"/>
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n"/>
+      <c r="F7" s="34" t="n"/>
+      <c r="G7" s="34" t="n"/>
+      <c r="H7" s="34" t="n"/>
+      <c r="I7" s="34" t="n"/>
+      <c r="J7" s="34" t="n"/>
+      <c r="K7" s="34" t="n"/>
+      <c r="L7" s="34" t="n"/>
+      <c r="M7" s="34" t="n"/>
+      <c r="N7" s="35" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="B8" s="31" t="n"/>
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>Project ID:</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>69-PUT</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>Start Test Date :</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="H8" s="39" t="n"/>
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="14" t="inlineStr">
+      <c r="J8" s="17" t="n"/>
+      <c r="K8" s="17" t="n"/>
+      <c r="L8" s="17" t="n"/>
+      <c r="M8" s="17" t="n"/>
+      <c r="N8" s="35" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="B9" s="31" t="n"/>
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="34" t="n"/>
+      <c r="G9" s="34" t="n"/>
+      <c r="H9" s="34" t="n"/>
+      <c r="I9" s="34" t="n"/>
+      <c r="J9" s="34" t="n"/>
+      <c r="K9" s="34" t="n"/>
+      <c r="L9" s="34" t="n"/>
+      <c r="M9" s="34" t="n"/>
+      <c r="N9" s="35" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="B10" s="31" t="n"/>
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>Tester Name :</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t>Finish Test Date :</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="H10" s="39" t="n"/>
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="C12" s="14" t="inlineStr">
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="17" t="n"/>
+      <c r="L10" s="17" t="n"/>
+      <c r="M10" s="17" t="n"/>
+      <c r="N10" s="35" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+      <c r="H11" s="34" t="n"/>
+      <c r="I11" s="34" t="n"/>
+      <c r="J11" s="34" t="n"/>
+      <c r="K11" s="34" t="n"/>
+      <c r="L11" s="34" t="n"/>
+      <c r="M11" s="34" t="n"/>
+      <c r="N11" s="35" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>Project Release / Version :</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>Module / Function:</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>User &amp; Customer Module / Restaurant Review (รีวิวและให้คะแนน)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Module / Function: </t>
+        </is>
+      </c>
+      <c r="H12" s="39" t="n"/>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>Test Case Review</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="n"/>
+      <c r="K12" s="17" t="n"/>
+      <c r="L12" s="17" t="n"/>
+      <c r="M12" s="17" t="n"/>
+      <c r="N12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="37" t="n"/>
+      <c r="H13" s="37" t="n"/>
+      <c r="I13" s="37" t="n"/>
+      <c r="J13" s="37" t="n"/>
+      <c r="K13" s="37" t="n"/>
+      <c r="L13" s="37" t="n"/>
+      <c r="M13" s="37" t="n"/>
+      <c r="N13" s="38" t="n"/>
+    </row>
+    <row r="14" ht="14" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve"> FUNCTIONAL REQUIREMENTS (Requirements No.) :</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="C15" s="39" t="n"/>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="40" t="inlineStr">
         <is>
           <t>REQ-REV-001</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="6" t="inlineStr">
+      <c r="F15" s="40" t="n"/>
+      <c r="G15" s="40" t="n"/>
+      <c r="H15" s="40" t="n"/>
+    </row>
+    <row r="16" ht="12" customHeight="1"/>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>Test Case Objective</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>Test Step</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>Automate</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>Req No.</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t>Platforms</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr">
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>Updated By</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="8" t="inlineStr">
+    <row r="18" ht="114" customHeight="1">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>69AA3001</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการส่งรีวิวและให้คะแนนด้วยข้อมูลที่ถูกต้อง</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>1. เข้าสู่ระบบและไปที่หน้ารายละเอียดร้านอาหาร
 2. กดปุ่ม 'เขียนรีวิว'
@@ -3201,225 +5116,250 @@
 4. กด 'ส่งรีวิว'</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="42" t="inlineStr">
         <is>
           <t>คะแนน: 5 ดาว, ข้อความ: 'อาหารอร่อยมาก บริการดี', รูปภาพ: 2 รูป (JPEG, 2MB)</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="42" t="inlineStr">
         <is>
           <t>ระบบบันทึกรีวิวสำเร็จ แสดงผลในหน้าร้านค้า และคำนวณคะแนนเฉลี่ยใหม่แบบ Asynchronous</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="42" t="inlineStr"/>
+      <c r="I18" s="41" t="inlineStr"/>
+      <c r="J18" s="42" t="inlineStr">
         <is>
           <t>[Priority: P1 Critical | Risk Level: Medium]</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="K18" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="L18" s="41" t="inlineStr">
         <is>
           <t>REQ-REV-001</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="M18" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="N18" s="41" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="8" t="inlineStr">
+    <row r="19" ht="76" customHeight="1">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>69AA3002</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการจำกัดจำนวนรูปภาพในการรีวิว</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>1. เข้าหน้าเขียนรีวิว
 2. เลือกรูปภาพจำนวน 5 รูป
 3. พยายามเลือกรูปภาพที่ 6</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="42" t="inlineStr">
         <is>
           <t>รูปภาพจำนวน 6 รูป</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="41" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="42" t="inlineStr">
         <is>
           <t>ระบบแสดงข้อความ 'อัปโหลดรูปภาพได้สูงสุด 5 รูป' และไม่อนุญาตให้เลือกรูปเพิ่ม</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H19" s="42" t="inlineStr"/>
+      <c r="I19" s="41" t="inlineStr"/>
+      <c r="J19" s="42" t="inlineStr">
         <is>
           <t>[Priority: P3 Minor | Risk Level: Low] Boundary Value</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="K19" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="L19" s="41" t="inlineStr">
         <is>
           <t>REQ-REV-001</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="M19" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
+      <c r="N19" s="41" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="8" t="inlineStr">
+    <row r="20" ht="76" customHeight="1">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>69AA3003</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการบล็อกข้อความรีวิวที่มีคำหยาบคาย (Profanity Check)</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>1. เข้าหน้าเขียนรีวิว
 2. พิมพ์ข้อความที่มีคำหยาบตาม Blacklist
 3. กด 'ส่งรีวิว'</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="42" t="inlineStr">
         <is>
           <t>ข้อความ: 'ร้านนี้ห่วยแตก [คำหยาบ]'</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="41" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="42" t="inlineStr">
         <is>
           <t>ระบบบล็อกการส่งและแสดงข้อความแจ้งเตือน 'กรุณาแก้ไขคำที่ไม่เหมาะสม'</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="42" t="inlineStr"/>
+      <c r="I20" s="41" t="inlineStr"/>
+      <c r="J20" s="42" t="inlineStr">
         <is>
           <t>[Priority: P2 Major | Risk Level: Medium]</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="K20" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="L20" s="41" t="inlineStr">
         <is>
           <t>REQ-REV-001</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="M20" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="N20" s="41" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="8" t="inlineStr">
+    <row r="21" ht="76" customHeight="1">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>69AA3004</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการป้องกันผู้ใช้ที่ไม่ได้เข้าสู่ระบบในการเขียนรีวิว</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="42" t="inlineStr">
         <is>
           <t>1. ใช้งานแอปพลิเคชันในฐานะ Guest
 2. ไปที่หน้ารายละเอียดร้านอาหาร
 3. กดปุ่ม 'เขียนรีวิว'</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="42" t="inlineStr">
         <is>
           <t>Session = Null</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="41" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="42" t="inlineStr">
         <is>
           <t>ระบบแสดงข้อความ 'กรุณาเข้าสู่ระบบก่อนเขียนรีวิว' และนำผู้ใช้ไปยังหน้า Login</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H21" s="42" t="inlineStr"/>
+      <c r="I21" s="41" t="inlineStr"/>
+      <c r="J21" s="42" t="inlineStr">
         <is>
           <t>[Priority: P2 Major | Risk Level: Medium]</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="K21" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="L21" s="41" t="inlineStr">
         <is>
           <t>REQ-REV-001</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr">
+      <c r="M21" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L21" s="8" t="inlineStr">
+      <c r="N21" s="41" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="I12:M12"/>
+    <mergeCell ref="B1:N4"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:M10"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="D10:F10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3430,365 +5370,575 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L20"/>
+  <dimension ref="B1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+      <c r="J1" s="15" t="n"/>
+      <c r="K1" s="15" t="n"/>
+      <c r="L1" s="15" t="n"/>
+      <c r="M1" s="15" t="n"/>
+      <c r="N1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+      <c r="J2" s="15" t="n"/>
+      <c r="K2" s="15" t="n"/>
+      <c r="L2" s="15" t="n"/>
+      <c r="M2" s="15" t="n"/>
+      <c r="N2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="15" t="n"/>
+      <c r="H3" s="15" t="n"/>
+      <c r="I3" s="15" t="n"/>
+      <c r="J3" s="15" t="n"/>
+      <c r="K3" s="15" t="n"/>
+      <c r="L3" s="15" t="n"/>
+      <c r="M3" s="15" t="n"/>
+      <c r="N3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n"/>
+      <c r="I4" s="15" t="n"/>
+      <c r="J4" s="15" t="n"/>
+      <c r="K4" s="15" t="n"/>
+      <c r="L4" s="15" t="n"/>
+      <c r="M4" s="15" t="n"/>
+      <c r="N4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="29" t="n"/>
+      <c r="I5" s="29" t="n"/>
+      <c r="J5" s="29" t="n"/>
+      <c r="K5" s="29" t="n"/>
+      <c r="L5" s="29" t="n"/>
+      <c r="M5" s="29" t="n"/>
+      <c r="N5" s="30" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="B6" s="31" t="n"/>
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>Project Name :</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>FoodSmile</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="32" t="inlineStr">
         <is>
           <t>Create Date :</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="H6" s="39" t="n"/>
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="14" t="inlineStr">
+      <c r="J6" s="17" t="n"/>
+      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="17" t="n"/>
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="35" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="B7" s="31" t="n"/>
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n"/>
+      <c r="F7" s="34" t="n"/>
+      <c r="G7" s="34" t="n"/>
+      <c r="H7" s="34" t="n"/>
+      <c r="I7" s="34" t="n"/>
+      <c r="J7" s="34" t="n"/>
+      <c r="K7" s="34" t="n"/>
+      <c r="L7" s="34" t="n"/>
+      <c r="M7" s="34" t="n"/>
+      <c r="N7" s="35" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="B8" s="31" t="n"/>
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>Project ID:</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>69-PUT</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>Start Test Date :</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="H8" s="39" t="n"/>
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="14" t="inlineStr">
+      <c r="J8" s="17" t="n"/>
+      <c r="K8" s="17" t="n"/>
+      <c r="L8" s="17" t="n"/>
+      <c r="M8" s="17" t="n"/>
+      <c r="N8" s="35" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="B9" s="31" t="n"/>
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="34" t="n"/>
+      <c r="G9" s="34" t="n"/>
+      <c r="H9" s="34" t="n"/>
+      <c r="I9" s="34" t="n"/>
+      <c r="J9" s="34" t="n"/>
+      <c r="K9" s="34" t="n"/>
+      <c r="L9" s="34" t="n"/>
+      <c r="M9" s="34" t="n"/>
+      <c r="N9" s="35" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="B10" s="31" t="n"/>
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>Tester Name :</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t>Finish Test Date :</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="H10" s="39" t="n"/>
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="C12" s="14" t="inlineStr">
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="17" t="n"/>
+      <c r="L10" s="17" t="n"/>
+      <c r="M10" s="17" t="n"/>
+      <c r="N10" s="35" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+      <c r="H11" s="34" t="n"/>
+      <c r="I11" s="34" t="n"/>
+      <c r="J11" s="34" t="n"/>
+      <c r="K11" s="34" t="n"/>
+      <c r="L11" s="34" t="n"/>
+      <c r="M11" s="34" t="n"/>
+      <c r="N11" s="35" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>Project Release / Version :</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>Module / Function:</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>Merchant Module / Merchant Onboarding (ลงทะเบียนร้านค้า)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Module / Function: </t>
+        </is>
+      </c>
+      <c r="H12" s="39" t="n"/>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>Test Case Merchant Onboarding</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="n"/>
+      <c r="K12" s="17" t="n"/>
+      <c r="L12" s="17" t="n"/>
+      <c r="M12" s="17" t="n"/>
+      <c r="N12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="37" t="n"/>
+      <c r="H13" s="37" t="n"/>
+      <c r="I13" s="37" t="n"/>
+      <c r="J13" s="37" t="n"/>
+      <c r="K13" s="37" t="n"/>
+      <c r="L13" s="37" t="n"/>
+      <c r="M13" s="37" t="n"/>
+      <c r="N13" s="38" t="n"/>
+    </row>
+    <row r="14" ht="14" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve"> FUNCTIONAL REQUIREMENTS (Requirements No.) :</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="C15" s="39" t="n"/>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="40" t="inlineStr">
         <is>
           <t>REQ-MCH-001</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="6" t="inlineStr">
+      <c r="F15" s="40" t="n"/>
+      <c r="G15" s="40" t="n"/>
+      <c r="H15" s="40" t="n"/>
+    </row>
+    <row r="16" ht="12" customHeight="1"/>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>Test Case Objective</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>Test Step</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>Automate</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>Req No.</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t>Platforms</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr">
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>Updated By</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="8" t="inlineStr">
+    <row r="18" ht="76" customHeight="1">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>69AA4001</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการสร้างร้านค้าใหม่ที่ไม่ซ้ำซ้อนในระบบ</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>1. เข้าสู่ระบบในฐานะ Merchant
 2. กรอกข้อมูลร้านค้าใหม่และพิกัด GPS
 3. กด 'สร้างร้านค้า'</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="42" t="inlineStr">
         <is>
           <t>ชื่อร้าน: 'คาเฟ่แมวเหมียว', พิกัด: ห่างจากร้านอื่น &gt; 100 เมตร</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="42" t="inlineStr">
         <is>
           <t>ระบบบันทึกข้อมูลร้านค้าในสถานะ Pending Review สำเร็จ และให้ Merchant อัปโหลดเอกสาร KYC</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="42" t="inlineStr"/>
+      <c r="I18" s="41" t="inlineStr"/>
+      <c r="J18" s="42" t="inlineStr">
         <is>
           <t>[Priority: P1 Critical | Risk Level: High]</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="K18" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="L18" s="41" t="inlineStr">
         <is>
           <t>REQ-MCH-001</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="M18" s="41" t="inlineStr">
         <is>
           <t>Web Application</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="N18" s="41" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="8" t="inlineStr">
+    <row r="19" ht="95" customHeight="1">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>69AA4002</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบระบบป้องกันการสร้างร้านค้าซ้ำซ้อน (Duplicate Check)</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>1. กรอกชื่อร้านค้าที่คล้ายกับร้านที่มีอยู่แล้ว (&gt;= 85%)
 2. ระบุพิกัด GPS ที่ใกล้เคียงร้านเดิม (&lt;= 20 เมตร)
 3. กด 'ตรวจสอบข้อมูล'</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="42" t="inlineStr">
         <is>
           <t>ชื่อร้าน: 'ร้านอาหารตามสั่ง เจ๊จู', พิกัด: ห่างจากร้านเดิม 10 เมตร</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="41" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="42" t="inlineStr">
         <is>
           <t>ระบบแจ้งเตือนว่าพบร้านซ้ำซ้อน และแสดงปุ่ม 'อ้างสิทธิ์ (Claim)' แทนการสร้างใหม่</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H19" s="42" t="inlineStr"/>
+      <c r="I19" s="41" t="inlineStr"/>
+      <c r="J19" s="42" t="inlineStr">
         <is>
           <t>[Priority: P1 Critical | Risk Level: High]</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="K19" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="L19" s="41" t="inlineStr">
         <is>
           <t>REQ-MCH-001</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="M19" s="41" t="inlineStr">
         <is>
           <t>Web Application</t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
+      <c r="N19" s="41" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="8" t="inlineStr">
+    <row r="20" ht="95" customHeight="1">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>69AA4003</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการส่งคำขออ้างสิทธิ์ (Claim) ร้านค้าพร้อมเอกสาร KYC</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>1. กดปุ่ม 'อ้างสิทธิ์ (Claim)' จากร้านที่ระบบตรวจพบ
 2. อัปโหลดเอกสาร KYC (เช่น ภ.พ.20)
 3. กดส่งคำขอ</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="42" t="inlineStr">
         <is>
           <t>ไฟล์เอกสาร KYC (PDF, 5MB)</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="42" t="inlineStr">
         <is>
           <t>ระบบส่งคำขอ Claim ไปยัง Admin เพื่อตรวจสอบ (Manual Review) และแสดงสถานะรอการอนุมัติ</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="42" t="inlineStr"/>
+      <c r="I20" s="41" t="inlineStr"/>
+      <c r="J20" s="42" t="inlineStr">
         <is>
           <t>[Priority: P2 Major | Risk Level: Medium]</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="K20" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="L20" s="41" t="inlineStr">
         <is>
           <t>REQ-MCH-001</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="M20" s="41" t="inlineStr">
         <is>
           <t>Web Application</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="N20" s="41" t="inlineStr">
         <is>
           <t>Lead QA Architect</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="I12:M12"/>
+    <mergeCell ref="B1:N4"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:M10"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="D10:F10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>